--- a/data/trans_orig/IP13_R2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si limitaron su actividad por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54002</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>49166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>100640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111843</t>
+          <t>111364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433694</t>
+          <t>434378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447623</t>
+          <t>448593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489139</t>
+          <t>489980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504204</t>
+          <t>504436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>930020</t>
+          <t>928713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>949147</t>
+          <t>948885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>26583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>137126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146608</t>
+          <t>146379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163971</t>
+          <t>164536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176507</t>
+          <t>176512</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306644</t>
+          <t>305593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320995</t>
+          <t>320732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>36312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>77434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626795</t>
+          <t>627611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644813</t>
+          <t>644606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713777</t>
+          <t>712732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>734977</t>
+          <t>733763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1347712</t>
+          <t>1347737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP13_R2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12339</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6615</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49830</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53202</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51953</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48063</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54010</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54906</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>40365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106859</t>
+          <t>93996</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100640</t>
+          <t>87438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111364</t>
+          <t>98153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11070</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23491</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17843</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11101</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25316</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>24717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>43679</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>458790</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>452187</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>464608</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>441851</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>434378</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>448593</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>498028</t>
+          <t>414449</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489980</t>
+          <t>406885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504436</t>
+          <t>419706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>939880</t>
+          <t>873239</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>928713</t>
+          <t>863601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>948885</t>
+          <t>881797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10445</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17522</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3172</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>25741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157437</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150360</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161809</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>143261</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137126</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>146379</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>171761</t>
+          <t>143482</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164536</t>
+          <t>137625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176512</t>
+          <t>147027</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>315022</t>
+          <t>300919</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>305593</t>
+          <t>292117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320732</t>
+          <t>306781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34234</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44933</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19317</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36312</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51064</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77434</t>
+          <t>75809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>666059</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>655360</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>674279</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>637065</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>627611</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>644606</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>724695</t>
+          <t>602097</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>712732</t>
+          <t>593270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733763</t>
+          <t>609499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1361760</t>
+          <t>1268156</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1347737</t>
+          <t>1252820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1374107</t>
+          <t>1279413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
